--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98445</v>
+        <v>98455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98461</v>
+        <v>98463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98463</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98482</v>
+        <v>98485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -1865,7 +1865,7 @@
         <v>137256123</v>
       </c>
       <c r="B13" t="n">
-        <v>98485</v>
+        <v>98489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
